--- a/01_analyses_states/Telangana/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Telangana/results/SoIB_summaries.xlsx
@@ -396,7 +396,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C8">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2">
-        <v>70.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2">
-        <v>77.7</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>29.1</v>
+        <v>28.2</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/Telangana/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Telangana/results/SoIB_summaries.xlsx
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C8">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>2</v>

--- a/01_analyses_states/Telangana/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Telangana/results/SoIB_summaries.xlsx
@@ -393,13 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -430,6 +436,9 @@
       <c r="C4">
         <v>0</v>
       </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
       <c r="E4">
         <v>0</v>
       </c>
@@ -446,6 +455,9 @@
       <c r="C5">
         <v>0</v>
       </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -462,6 +474,9 @@
       <c r="C6">
         <v>0</v>
       </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -476,7 +491,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C8">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
@@ -675,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -688,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>71.8</v>
+        <v>72.8</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>78.7</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>28.2</v>
+        <v>27.2</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
     </row>
   </sheetData>
